--- a/ProductionBuild/autos.result.xlsx
+++ b/ProductionBuild/autos.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,400 +394,163 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Autoliv Inc</t>
+          <t>Bayerische Motoren Werke Aktiengesellschaft</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ALV</t>
+          <t>BMWKY</t>
         </is>
       </c>
       <c r="C2">
-        <v>1.924296545454546</v>
+        <v>1.6029</v>
       </c>
       <c r="D2">
-        <v>21.167262</v>
+        <v>16.029</v>
       </c>
       <c r="E2">
-        <v>81.52017211914063</v>
+        <v>31.01000022888184</v>
       </c>
       <c r="F2">
-        <v>116.1699981689453</v>
+        <v>31.93000030517578</v>
       </c>
       <c r="G2">
-        <v>34.64982604980469</v>
+        <v>0.9200000762939453</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aisin Corporation</t>
+          <t>Great Wall Motor Company Limited</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASEKY</t>
+          <t>GWLLY</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.2011665</v>
+        <v>0.4311</v>
       </c>
       <c r="D3">
-        <v>0.402333</v>
+        <v>4.311</v>
       </c>
       <c r="E3">
-        <v>15.03166675567627</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="F3">
-        <v>15.52999973297119</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="G3">
-        <v>0.4983329772949219</v>
+        <v>7.380000114440918</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bayerische Motoren Werke Aktiengesellschaft</t>
+          <t>Honda Motor Co Ltd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BMWKY</t>
+          <t>HMC</t>
         </is>
       </c>
       <c r="C4">
-        <v>1.6029</v>
+        <v>0.7852</v>
       </c>
       <c r="D4">
-        <v>16.029</v>
+        <v>7.852</v>
       </c>
       <c r="E4">
-        <v>31.01000022888184</v>
+        <v>29.19000053405762</v>
       </c>
       <c r="F4">
-        <v>31.93000030517578</v>
+        <v>24.6200008392334</v>
       </c>
       <c r="G4">
-        <v>0.9200000762939453</v>
+        <v>-4.569999694824219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gentex Corporation</t>
+          <t>Isuzu Motors Ltd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GNTX</t>
+          <t>ISUZY</t>
         </is>
       </c>
       <c r="C5">
-        <v>0.4145454545454546</v>
+        <v>0.3115</v>
       </c>
       <c r="D5">
-        <v>4.56</v>
+        <v>0.623</v>
       </c>
       <c r="E5">
-        <v>19.69000053405762</v>
+        <v>12.52999973297119</v>
       </c>
       <c r="F5">
-        <v>22.76000022888184</v>
+        <v>14.46000003814697</v>
       </c>
       <c r="G5">
-        <v>3.069999694824219</v>
+        <v>1.930000305175781</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Great Wall Motor Company Limited</t>
+          <t>Mercedes Benz Group AG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GWLLY</t>
+          <t>MBGYY</t>
         </is>
       </c>
       <c r="C6">
-        <v>0.4311</v>
+        <v>1.45305</v>
       </c>
       <c r="D6">
-        <v>4.311</v>
+        <v>14.5305</v>
       </c>
       <c r="E6">
-        <v>9.220000267028809</v>
+        <v>18.58749961853027</v>
       </c>
       <c r="F6">
-        <v>16.60000038146973</v>
+        <v>14.72999954223633</v>
       </c>
       <c r="G6">
-        <v>7.380000114440918</v>
+        <v>-3.857500076293945</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Honda Motor Co Ltd</t>
+          <t>Compagnie Generale des Etablissements Michelin Soc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HMC</t>
+          <t>MGDDY</t>
         </is>
       </c>
       <c r="C7">
-        <v>0.7852</v>
+        <v>0.53215</v>
       </c>
       <c r="D7">
-        <v>7.852</v>
+        <v>5.3215</v>
       </c>
       <c r="E7">
-        <v>29.19000053405762</v>
+        <v>13.88125038146973</v>
       </c>
       <c r="F7">
-        <v>24.6200008392334</v>
+        <v>18.59000015258789</v>
       </c>
       <c r="G7">
-        <v>-4.569999694824219</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Isuzu Motors Ltd</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ISUZY</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0.3115</v>
-      </c>
-      <c r="D8">
-        <v>0.623</v>
-      </c>
-      <c r="E8">
-        <v>12.52999973297119</v>
-      </c>
-      <c r="F8">
-        <v>14.46000003814697</v>
-      </c>
-      <c r="G8">
-        <v>1.930000305175781</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Koito Manufacturing Co Ltd</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>KOTMY</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.1895</v>
-      </c>
-      <c r="D9">
-        <v>0.379</v>
-      </c>
-      <c r="F9">
-        <v>15.22000026702881</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lear Corp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>LEA</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>2.234545454545454</v>
-      </c>
-      <c r="D10">
-        <v>24.58</v>
-      </c>
-      <c r="E10">
-        <v>132.3699951171875</v>
-      </c>
-      <c r="F10">
-        <v>128.0700073242188</v>
-      </c>
-      <c r="G10">
-        <v>-4.29998779296875</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mercedes Benz Group AG</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MBGYY</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>1.45305</v>
-      </c>
-      <c r="D11">
-        <v>14.5305</v>
-      </c>
-      <c r="E11">
-        <v>18.58749961853027</v>
-      </c>
-      <c r="F11">
-        <v>14.72999954223633</v>
-      </c>
-      <c r="G11">
-        <v>-3.857500076293945</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Magna International Inc</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MGA</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>1.403636363636364</v>
-      </c>
-      <c r="D12">
-        <v>15.44</v>
-      </c>
-      <c r="E12">
-        <v>43.40000152587891</v>
-      </c>
-      <c r="F12">
-        <v>61.38000106811523</v>
-      </c>
-      <c r="G12">
-        <v>17.97999954223633</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Compagnie Generale des Etablissements Michelin Soc</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MGDDY</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0.53215</v>
-      </c>
-      <c r="D13">
-        <v>5.3215</v>
-      </c>
-      <c r="E13">
-        <v>13.88125038146973</v>
-      </c>
-      <c r="F13">
-        <v>18.59000015258789</v>
-      </c>
-      <c r="G13">
         <v>4.708749771118164</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Suzuki Motor Corp</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SZKMY</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>0.5575</v>
-      </c>
-      <c r="D14">
-        <v>1.115</v>
-      </c>
-      <c r="E14">
-        <v>35.5625</v>
-      </c>
-      <c r="F14">
-        <v>45.66999816894531</v>
-      </c>
-      <c r="G14">
-        <v>10.10749816894531</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>THOR Industries Inc</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>THO</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>1.536363636363636</v>
-      </c>
-      <c r="D15">
-        <v>16.9</v>
-      </c>
-      <c r="E15">
-        <v>100.0500030517578</v>
-      </c>
-      <c r="F15">
-        <v>78</v>
-      </c>
-      <c r="G15">
-        <v>-22.05000305175781</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Toyota Motor Corp</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TM</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>3.7484</v>
-      </c>
-      <c r="D16">
-        <v>37.484</v>
-      </c>
-      <c r="E16">
-        <v>117.1999969482422</v>
-      </c>
-      <c r="F16">
-        <v>200.4299926757813</v>
-      </c>
-      <c r="G16">
-        <v>83.22999572753906</v>
       </c>
     </row>
   </sheetData>

--- a/ProductionBuild/autos.result.xlsx
+++ b/ProductionBuild/autos.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,190 +367,925 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>avgdividend</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>totaldividends</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>price_end</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>change</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturn</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturnover10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>shares500</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>totalspend</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyearequityproj</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyeardivproj</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>totalfiveyearview</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bayerische Motoren Werke Aktiengesellschaft</t>
+          <t>Toyota Motor Corp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BMWKY</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1.6029</v>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
       </c>
       <c r="D2">
-        <v>16.029</v>
+        <v>3.7484</v>
       </c>
       <c r="E2">
-        <v>31.01000022888184</v>
+        <v>37.484</v>
       </c>
       <c r="F2">
-        <v>31.93000030517578</v>
+        <v>117.1999969482422</v>
       </c>
       <c r="G2">
-        <v>0.9200000762939453</v>
+        <v>196.0800018310547</v>
+      </c>
+      <c r="H2">
+        <v>78.8800048828125</v>
+      </c>
+      <c r="I2">
+        <v>116.3640048828125</v>
+      </c>
+      <c r="J2">
+        <v>11.63640048828125</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>588.2400054931641</v>
+      </c>
+      <c r="M2">
+        <v>58.18200244140625</v>
+      </c>
+      <c r="N2">
+        <v>18.742</v>
+      </c>
+      <c r="O2">
+        <v>76.92400244140626</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Great Wall Motor Company Limited</t>
+          <t>Autoliv Inc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GWLLY</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0.4311</v>
+          <t>ALV</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
       </c>
       <c r="D3">
-        <v>4.311</v>
+        <v>1.924296545454546</v>
       </c>
       <c r="E3">
-        <v>9.220000267028809</v>
+        <v>21.167262</v>
       </c>
       <c r="F3">
-        <v>16.60000038146973</v>
+        <v>81.52017211914063</v>
       </c>
       <c r="G3">
-        <v>7.380000114440918</v>
+        <v>116.3099975585938</v>
+      </c>
+      <c r="H3">
+        <v>34.78982543945313</v>
+      </c>
+      <c r="I3">
+        <v>55.95708743945313</v>
+      </c>
+      <c r="J3">
+        <v>5.595708743945313</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>581.5499877929688</v>
+      </c>
+      <c r="M3">
+        <v>27.97854371972656</v>
+      </c>
+      <c r="N3">
+        <v>9.621482727272728</v>
+      </c>
+      <c r="O3">
+        <v>37.60002644699929</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Honda Motor Co Ltd</t>
+          <t>Magna International Inc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMC</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.7852</v>
+          <t>MGA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
       </c>
       <c r="D4">
-        <v>7.852</v>
+        <v>1.403636363636364</v>
       </c>
       <c r="E4">
-        <v>29.19000053405762</v>
+        <v>15.44</v>
       </c>
       <c r="F4">
-        <v>24.6200008392334</v>
+        <v>43.40000152587891</v>
       </c>
       <c r="G4">
-        <v>-4.569999694824219</v>
+        <v>62.20000076293945</v>
+      </c>
+      <c r="H4">
+        <v>18.79999923706055</v>
+      </c>
+      <c r="I4">
+        <v>34.23999923706054</v>
+      </c>
+      <c r="J4">
+        <v>3.423999923706055</v>
+      </c>
+      <c r="K4">
+        <v>9</v>
+      </c>
+      <c r="L4">
+        <v>559.8000068664551</v>
+      </c>
+      <c r="M4">
+        <v>17.11999961853027</v>
+      </c>
+      <c r="N4">
+        <v>7.018181818181818</v>
+      </c>
+      <c r="O4">
+        <v>24.13818143671209</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Isuzu Motors Ltd</t>
+          <t>Lear Corp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ISUZY</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.3115</v>
+          <t>LEA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
       </c>
       <c r="D5">
-        <v>0.623</v>
+        <v>2.234545454545454</v>
       </c>
       <c r="E5">
-        <v>12.52999973297119</v>
+        <v>24.58</v>
       </c>
       <c r="F5">
-        <v>14.46000003814697</v>
+        <v>132.3699951171875</v>
       </c>
       <c r="G5">
-        <v>1.930000305175781</v>
+        <v>129.7200012207031</v>
+      </c>
+      <c r="H5">
+        <v>-2.649993896484375</v>
+      </c>
+      <c r="I5">
+        <v>21.93000610351562</v>
+      </c>
+      <c r="J5">
+        <v>2.193000610351562</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>518.8800048828125</v>
+      </c>
+      <c r="M5">
+        <v>10.96500305175781</v>
+      </c>
+      <c r="N5">
+        <v>11.17272727272727</v>
+      </c>
+      <c r="O5">
+        <v>22.13773032448508</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mercedes Benz Group AG</t>
+          <t>Bayerische Motoren Werke Aktiengesellschaft</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MBGYY</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>1.45305</v>
+          <t>BMWKY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
       </c>
       <c r="D6">
-        <v>14.5305</v>
+        <v>1.6029</v>
       </c>
       <c r="E6">
-        <v>18.58749961853027</v>
+        <v>16.029</v>
       </c>
       <c r="F6">
-        <v>14.72999954223633</v>
+        <v>31.01000022888184</v>
       </c>
       <c r="G6">
-        <v>-3.857500076293945</v>
+        <v>31.43000030517578</v>
+      </c>
+      <c r="H6">
+        <v>0.4200000762939453</v>
+      </c>
+      <c r="I6">
+        <v>16.44900007629395</v>
+      </c>
+      <c r="J6">
+        <v>1.644900007629394</v>
+      </c>
+      <c r="K6">
+        <v>16</v>
+      </c>
+      <c r="L6">
+        <v>502.8800048828125</v>
+      </c>
+      <c r="M6">
+        <v>8.224500038146973</v>
+      </c>
+      <c r="N6">
+        <v>8.0145</v>
+      </c>
+      <c r="O6">
+        <v>16.23900003814697</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Great Wall Motor Company Limited</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GWLLY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.4311</v>
+      </c>
+      <c r="E7">
+        <v>4.311</v>
+      </c>
+      <c r="F7">
+        <v>9.220000267028809</v>
+      </c>
+      <c r="G7">
+        <v>17.09700012207031</v>
+      </c>
+      <c r="H7">
+        <v>7.876999855041504</v>
+      </c>
+      <c r="I7">
+        <v>12.1879998550415</v>
+      </c>
+      <c r="J7">
+        <v>1.21879998550415</v>
+      </c>
+      <c r="K7">
+        <v>30</v>
+      </c>
+      <c r="L7">
+        <v>512.9100036621094</v>
+      </c>
+      <c r="M7">
+        <v>6.093999927520752</v>
+      </c>
+      <c r="N7">
+        <v>2.1555</v>
+      </c>
+      <c r="O7">
+        <v>8.249499927520752</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Suzuki Motor Corp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SZKMY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.5575</v>
+      </c>
+      <c r="E8">
+        <v>1.115</v>
+      </c>
+      <c r="F8">
+        <v>35.5625</v>
+      </c>
+      <c r="G8">
+        <v>45.06000137329102</v>
+      </c>
+      <c r="H8">
+        <v>9.497501373291016</v>
+      </c>
+      <c r="I8">
+        <v>10.61250137329102</v>
+      </c>
+      <c r="J8">
+        <v>1.061250137329102</v>
+      </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
+      <c r="L8">
+        <v>540.7200164794922</v>
+      </c>
+      <c r="M8">
+        <v>5.306250686645509</v>
+      </c>
+      <c r="N8">
+        <v>2.7875</v>
+      </c>
+      <c r="O8">
+        <v>8.093750686645508</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mercedes Benz Group AG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MBGYY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>1.45305</v>
+      </c>
+      <c r="E9">
+        <v>14.5305</v>
+      </c>
+      <c r="F9">
+        <v>18.58749961853027</v>
+      </c>
+      <c r="G9">
+        <v>14.63000011444092</v>
+      </c>
+      <c r="H9">
+        <v>-3.957499504089355</v>
+      </c>
+      <c r="I9">
+        <v>10.57300049591064</v>
+      </c>
+      <c r="J9">
+        <v>1.057300049591064</v>
+      </c>
+      <c r="K9">
+        <v>35</v>
+      </c>
+      <c r="L9">
+        <v>512.0500040054321</v>
+      </c>
+      <c r="M9">
+        <v>5.286500247955322</v>
+      </c>
+      <c r="N9">
+        <v>7.26525</v>
+      </c>
+      <c r="O9">
+        <v>12.55175024795532</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Compagnie Generale des Etablissements Michelin Soc</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>MGDDY</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D10">
         <v>0.53215</v>
       </c>
-      <c r="D7">
+      <c r="E10">
         <v>5.3215</v>
       </c>
-      <c r="E7">
+      <c r="F10">
         <v>13.88125038146973</v>
       </c>
-      <c r="F7">
-        <v>18.59000015258789</v>
-      </c>
-      <c r="G7">
-        <v>4.708749771118164</v>
+      <c r="G10">
+        <v>18.61000061035156</v>
+      </c>
+      <c r="H10">
+        <v>4.728750228881836</v>
+      </c>
+      <c r="I10">
+        <v>10.05025022888184</v>
+      </c>
+      <c r="J10">
+        <v>1.005025022888184</v>
+      </c>
+      <c r="K10">
+        <v>27</v>
+      </c>
+      <c r="L10">
+        <v>502.4700164794922</v>
+      </c>
+      <c r="M10">
+        <v>5.025125114440918</v>
+      </c>
+      <c r="N10">
+        <v>2.66075</v>
+      </c>
+      <c r="O10">
+        <v>7.685875114440918</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gentex Corporation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GNTX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.4145454545454546</v>
+      </c>
+      <c r="E11">
+        <v>4.56</v>
+      </c>
+      <c r="F11">
+        <v>19.69000053405762</v>
+      </c>
+      <c r="G11">
+        <v>23.03000068664551</v>
+      </c>
+      <c r="H11">
+        <v>3.340000152587891</v>
+      </c>
+      <c r="I11">
+        <v>7.90000015258789</v>
+      </c>
+      <c r="J11">
+        <v>0.790000015258789</v>
+      </c>
+      <c r="K11">
+        <v>22</v>
+      </c>
+      <c r="L11">
+        <v>506.6600151062012</v>
+      </c>
+      <c r="M11">
+        <v>3.950000076293945</v>
+      </c>
+      <c r="N11">
+        <v>2.072727272727273</v>
+      </c>
+      <c r="O11">
+        <v>6.022727349021218</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Honda Motor Co Ltd</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HMC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.7852</v>
+      </c>
+      <c r="E12">
+        <v>7.852</v>
+      </c>
+      <c r="F12">
+        <v>29.19000053405762</v>
+      </c>
+      <c r="G12">
+        <v>24.47999954223633</v>
+      </c>
+      <c r="H12">
+        <v>-4.710000991821289</v>
+      </c>
+      <c r="I12">
+        <v>3.141999008178711</v>
+      </c>
+      <c r="J12">
+        <v>0.3141999008178711</v>
+      </c>
+      <c r="K12">
+        <v>21</v>
+      </c>
+      <c r="L12">
+        <v>514.0799903869629</v>
+      </c>
+      <c r="M12">
+        <v>1.570999504089356</v>
+      </c>
+      <c r="N12">
+        <v>3.926</v>
+      </c>
+      <c r="O12">
+        <v>5.496999504089356</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Isuzu Motors Ltd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ISUZY</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.3115</v>
+      </c>
+      <c r="E13">
+        <v>0.623</v>
+      </c>
+      <c r="F13">
+        <v>12.52999973297119</v>
+      </c>
+      <c r="G13">
+        <v>14.14000034332275</v>
+      </c>
+      <c r="H13">
+        <v>1.610000610351563</v>
+      </c>
+      <c r="I13">
+        <v>2.233000610351563</v>
+      </c>
+      <c r="J13">
+        <v>0.2233000610351563</v>
+      </c>
+      <c r="K13">
+        <v>36</v>
+      </c>
+      <c r="L13">
+        <v>509.0400123596191</v>
+      </c>
+      <c r="M13">
+        <v>1.116500305175781</v>
+      </c>
+      <c r="N13">
+        <v>1.5575</v>
+      </c>
+      <c r="O13">
+        <v>2.674000305175781</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Aisin Corporation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ASEKY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.2011665</v>
+      </c>
+      <c r="E14">
+        <v>0.402333</v>
+      </c>
+      <c r="F14">
+        <v>15.03166675567627</v>
+      </c>
+      <c r="G14">
+        <v>15.1899995803833</v>
+      </c>
+      <c r="H14">
+        <v>0.1583328247070313</v>
+      </c>
+      <c r="I14">
+        <v>0.5606658247070313</v>
+      </c>
+      <c r="J14">
+        <v>0.05606658247070313</v>
+      </c>
+      <c r="K14">
+        <v>33</v>
+      </c>
+      <c r="L14">
+        <v>501.2699861526489</v>
+      </c>
+      <c r="M14">
+        <v>0.2803329123535157</v>
+      </c>
+      <c r="N14">
+        <v>1.0058325</v>
+      </c>
+      <c r="O14">
+        <v>1.286165412353516</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>THOR Industries Inc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>THO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>1.536363636363636</v>
+      </c>
+      <c r="E15">
+        <v>16.9</v>
+      </c>
+      <c r="F15">
+        <v>100.0500030517578</v>
+      </c>
+      <c r="G15">
+        <v>78.80999755859375</v>
+      </c>
+      <c r="H15">
+        <v>-21.24000549316406</v>
+      </c>
+      <c r="I15">
+        <v>-4.340005493164064</v>
+      </c>
+      <c r="J15">
+        <v>-0.4340005493164064</v>
+      </c>
+      <c r="K15">
+        <v>7</v>
+      </c>
+      <c r="L15">
+        <v>551.6699829101563</v>
+      </c>
+      <c r="M15">
+        <v>-2.170002746582032</v>
+      </c>
+      <c r="N15">
+        <v>7.681818181818182</v>
+      </c>
+      <c r="O15">
+        <v>5.51181543523615</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Koito Manufacturing Co Ltd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>KOTMY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>autos</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.1895</v>
+      </c>
+      <c r="E16">
+        <v>0.379</v>
+      </c>
+      <c r="G16">
+        <v>15.22000026702881</v>
+      </c>
+      <c r="K16">
+        <v>33</v>
+      </c>
+      <c r="L16">
+        <v>502.2600088119507</v>
+      </c>
+      <c r="N16">
+        <v>0.9475</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
   </sheetData>
